--- a/ZonasEscolares/excels/PIURA-PIURA-PIURA.xlsx
+++ b/ZonasEscolares/excels/PIURA-PIURA-PIURA.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3190,7 +3190,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3554,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3762,7 +3762,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4126,7 +4126,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4282,7 +4282,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4386,7 +4386,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4438,7 +4438,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4542,7 +4542,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4594,7 +4594,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4750,7 +4750,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4854,7 +4854,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4906,7 +4906,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5114,7 +5114,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5166,7 +5166,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5218,7 +5218,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/PIURA-PIURA-PIURA.xlsx
+++ b/ZonasEscolares/excels/PIURA-PIURA-PIURA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>001 MARIA CONCEPCION RAMOS CAMPOS</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-5.19929</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-80.63386</v>
-      </c>
-      <c r="I2" t="n">
-        <v>285</v>
-      </c>
-      <c r="J2" t="n">
-        <v>13</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-5.19929</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-80.63386</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>002</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-5.18936</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-80.63822</v>
-      </c>
-      <c r="I3" t="n">
-        <v>279</v>
-      </c>
-      <c r="J3" t="n">
-        <v>13</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-5.18936</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-80.63822</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>225</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-5.201211</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-80.632621</v>
-      </c>
-      <c r="I4" t="n">
-        <v>78</v>
-      </c>
-      <c r="J4" t="n">
-        <v>4</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-5.201211</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-80.632621</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>COMPLEJO LA ALBORADA</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-5.18634</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-80.65428</v>
-      </c>
-      <c r="I5" t="n">
-        <v>658</v>
-      </c>
-      <c r="J5" t="n">
-        <v>33</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-5.18634</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-80.65428</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>658</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>SELMIRA DE VARONA</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-5.19173</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-80.64987000000001</v>
-      </c>
-      <c r="I6" t="n">
-        <v>934</v>
-      </c>
-      <c r="J6" t="n">
-        <v>38</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-5.19173</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-80.64987</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>934</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>PNP BACILIO RAMIREZ PEÑA</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-5.18797</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-80.65006</v>
-      </c>
-      <c r="I7" t="n">
-        <v>860</v>
-      </c>
-      <c r="J7" t="n">
-        <v>40</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-5.18797</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-80.65006</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>860</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>14001 MAGDALENA SEMINARIO DE LLIROD</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-5.19625</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-80.6379</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1520</v>
-      </c>
-      <c r="J8" t="n">
-        <v>62</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-5.19625</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-80.6379</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1520</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>14007</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-5.19012</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-80.65418</v>
-      </c>
-      <c r="I9" t="n">
-        <v>804</v>
-      </c>
-      <c r="J9" t="n">
-        <v>34</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-5.19012</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-80.65418</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>804</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>ELVIRA CASTRO DE QUIROS</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-5.130262</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-80.641116</v>
-      </c>
-      <c r="I10" t="n">
-        <v>499</v>
-      </c>
-      <c r="J10" t="n">
-        <v>30</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-5.130262</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-80.641116</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>14103 / CPED - 14103</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-5.15807</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-80.62092</v>
-      </c>
-      <c r="I11" t="n">
-        <v>227</v>
-      </c>
-      <c r="J11" t="n">
-        <v>17</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-5.15807</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-80.62092</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>SAN PEDRO</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-5.2004</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-80.64155</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1383</v>
-      </c>
-      <c r="J12" t="n">
-        <v>65</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-5.2004</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-80.64155</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1383</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>15005</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-5.2045</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-80.63330000000001</v>
-      </c>
-      <c r="I13" t="n">
-        <v>390</v>
-      </c>
-      <c r="J13" t="n">
-        <v>14</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-5.2045</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-80.6333</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>390</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>VICTOR FRANCISCO ROSALES ORTEGA</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-5.18607</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-80.63382</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1232</v>
-      </c>
-      <c r="J14" t="n">
-        <v>50</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-5.18607</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-80.63382</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1232</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>FEDERICO HELGUERO SEMINARIO</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-5.174365</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-80.64591299999999</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1355</v>
-      </c>
-      <c r="J15" t="n">
-        <v>57</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-5.174365</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-80.645913</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1355</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>20001</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-5.044701</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-80.693657</v>
-      </c>
-      <c r="I16" t="n">
-        <v>242</v>
-      </c>
-      <c r="J16" t="n">
-        <v>15</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-5.044701</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-80.693657</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>20436 ROSA SUAREZ RAFAEL</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-5.183353</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-80.656988</v>
-      </c>
-      <c r="I17" t="n">
-        <v>443</v>
-      </c>
-      <c r="J17" t="n">
-        <v>20</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-5.183353</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-80.656988</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>20197</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-5.20372</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-80.63676</v>
-      </c>
-      <c r="I18" t="n">
-        <v>578</v>
-      </c>
-      <c r="J18" t="n">
-        <v>23</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-5.20372</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-80.63676</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>578</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>PARCEMON SALDARRIAGA MONTEJO</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-5.18826</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-80.62914000000001</v>
-      </c>
-      <c r="I19" t="n">
-        <v>890</v>
-      </c>
-      <c r="J19" t="n">
-        <v>35</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-5.18826</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-80.62914</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>890</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>ANN GOULDEN</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-5.20277</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-80.62900999999999</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1131</v>
-      </c>
-      <c r="J20" t="n">
-        <v>40</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-5.20277</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-80.62901</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1131</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>ROSA CARRERA DE MARTOS</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-5.18532</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-80.62804</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1062</v>
-      </c>
-      <c r="J21" t="n">
-        <v>42</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-5.18532</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-80.62804</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1062</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>IGNACIO MERINO</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-5.17923</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-80.64373999999999</v>
-      </c>
-      <c r="I22" t="n">
-        <v>1290</v>
-      </c>
-      <c r="J22" t="n">
-        <v>51</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-5.17923</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-80.64374</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1290</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>IGNACIO SANCHEZ</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-5.19302</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-80.62747</v>
-      </c>
-      <c r="I23" t="n">
-        <v>812</v>
-      </c>
-      <c r="J23" t="n">
-        <v>31</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-5.19302</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-80.62747</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>812</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-5.1876</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-80.62869000000001</v>
-      </c>
-      <c r="I24" t="n">
-        <v>1369</v>
-      </c>
-      <c r="J24" t="n">
-        <v>56</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-5.1876</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-80.62869</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1369</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>SAN MIGUEL</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-5.19615</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-80.6349</v>
-      </c>
-      <c r="I25" t="n">
-        <v>3429</v>
-      </c>
-      <c r="J25" t="n">
-        <v>163</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-5.19615</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-80.6349</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>3429</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>CORONEL JOSE JOAQUIN INCLAN</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-5.19926</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-80.63702000000001</v>
-      </c>
-      <c r="I26" t="n">
-        <v>1080</v>
-      </c>
-      <c r="J26" t="n">
-        <v>43</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-5.19926</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-80.63702</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>ENRIQUE LOPEZ ALBUJAR</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-5.19406</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-80.64891</v>
-      </c>
-      <c r="I27" t="n">
-        <v>1064</v>
-      </c>
-      <c r="J27" t="n">
-        <v>69</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-5.19406</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-80.64891</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1064</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-5.19006</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-80.63590000000001</v>
-      </c>
-      <c r="I28" t="n">
-        <v>1902</v>
-      </c>
-      <c r="J28" t="n">
-        <v>79</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-5.19006</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-80.6359</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1902</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>LOS ALGARROBOS</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-5.1679</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-80.64952</v>
-      </c>
-      <c r="I29" t="n">
-        <v>714</v>
-      </c>
-      <c r="J29" t="n">
-        <v>37</v>
-      </c>
-      <c r="K29" t="n">
-        <v>1</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-5.1679</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-80.64952</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>714</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>BELEN</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-5.19233</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-80.62737</v>
-      </c>
-      <c r="I30" t="n">
-        <v>982</v>
-      </c>
-      <c r="J30" t="n">
-        <v>50</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-5.19233</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-80.62737</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>982</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>DOMENICO SAVIO</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-5.1819</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-80.63531</v>
-      </c>
-      <c r="I31" t="n">
-        <v>170</v>
-      </c>
-      <c r="J31" t="n">
-        <v>18</v>
-      </c>
-      <c r="K31" t="n">
-        <v>1</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-5.1819</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-80.63531</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>LA SEMILLITA</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-5.17613</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-80.64111</v>
-      </c>
-      <c r="I32" t="n">
-        <v>442</v>
-      </c>
-      <c r="J32" t="n">
-        <v>27</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-5.17613</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-80.64111</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>442</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>LOS TALLANES</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-5.18228</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-80.6588</v>
-      </c>
-      <c r="I33" t="n">
-        <v>266</v>
-      </c>
-      <c r="J33" t="n">
-        <v>26</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-5.18228</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-80.6588</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2185,20 +2493,30 @@
           <t>NUESTRA SEÑORA DE LOURDES</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-5.1928</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-80.63403</v>
-      </c>
-      <c r="I34" t="n">
-        <v>1031</v>
-      </c>
-      <c r="J34" t="n">
-        <v>61</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-5.1928</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-80.63403</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1031</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2237,20 +2555,30 @@
           <t>SAN LUIS GONZAGA</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-5.181578</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-80.633864</v>
-      </c>
-      <c r="I35" t="n">
-        <v>318</v>
-      </c>
-      <c r="J35" t="n">
-        <v>34</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-5.181578</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-80.633864</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>318</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2289,20 +2617,30 @@
           <t>SANTA MARIA</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>-5.184422</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-80.62765</v>
-      </c>
-      <c r="I36" t="n">
-        <v>847</v>
-      </c>
-      <c r="J36" t="n">
-        <v>45</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-5.184422</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-80.62765</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>847</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2341,20 +2679,30 @@
           <t>STELLA MARIS</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>-5.19688</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-80.6301</v>
-      </c>
-      <c r="I37" t="n">
-        <v>235</v>
-      </c>
-      <c r="J37" t="n">
-        <v>14</v>
-      </c>
-      <c r="K37" t="n">
-        <v>1</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-5.19688</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-80.6301</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2393,20 +2741,30 @@
           <t>SUSANA WESLEY</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>-5.19983</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-80.63764999999999</v>
-      </c>
-      <c r="I38" t="n">
-        <v>449</v>
-      </c>
-      <c r="J38" t="n">
-        <v>15</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-5.19983</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-80.63765</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>449</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2445,20 +2803,30 @@
           <t>TURICARA</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>-5.169126</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-80.63548900000001</v>
-      </c>
-      <c r="I39" t="n">
-        <v>621</v>
-      </c>
-      <c r="J39" t="n">
-        <v>51</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-5.169126</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-80.635489</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2497,20 +2865,30 @@
           <t>ADVENTISTA PIURA</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>-5.19474</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-80.62961</v>
-      </c>
-      <c r="I40" t="n">
-        <v>386</v>
-      </c>
-      <c r="J40" t="n">
-        <v>24</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-5.19474</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-80.62961</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>386</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2549,20 +2927,30 @@
           <t>HOGAR SAN ANTONIO</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>-5.191628</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-80.63440900000001</v>
-      </c>
-      <c r="I41" t="n">
-        <v>630</v>
-      </c>
-      <c r="J41" t="n">
-        <v>42</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-5.191628</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-80.634409</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2601,20 +2989,30 @@
           <t>JOSE ANTONIO ENCINAS</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>-5.20017</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-80.63158</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" t="n">
-        <v>1</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-5.20017</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-80.63158</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2653,20 +3051,30 @@
           <t>VALLESOL</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>-5.17874</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-80.6327</v>
-      </c>
-      <c r="I43" t="n">
-        <v>1018</v>
-      </c>
-      <c r="J43" t="n">
-        <v>67</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-5.17874</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-80.6327</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1018</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2705,20 +3113,30 @@
           <t>MARIA MONTESSORI</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>-5.17481</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-80.6284</v>
-      </c>
-      <c r="I44" t="n">
-        <v>875</v>
-      </c>
-      <c r="J44" t="n">
-        <v>60</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-5.17481</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-80.6284</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>875</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2757,20 +3175,30 @@
           <t>LA SENDITA DE SANTA TERESITA DEL NIÑO JESUS</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>-5.19455</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-80.6319</v>
-      </c>
-      <c r="I45" t="n">
-        <v>12</v>
-      </c>
-      <c r="J45" t="n">
-        <v>1</v>
-      </c>
-      <c r="K45" t="n">
-        <v>1</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-5.19455</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-80.6319</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2809,20 +3237,30 @@
           <t>JOSE CARLOS MARIATEGUI LACHIRA</t>
         </is>
       </c>
-      <c r="G46" t="n">
-        <v>-5.280572</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-80.71472799999999</v>
-      </c>
-      <c r="I46" t="n">
-        <v>551</v>
-      </c>
-      <c r="J46" t="n">
-        <v>37</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-5.280572</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-80.714728</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>551</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2861,20 +3299,30 @@
           <t>FEDERICO VILLARREAL</t>
         </is>
       </c>
-      <c r="G47" t="n">
-        <v>-5.318774</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-80.663586</v>
-      </c>
-      <c r="I47" t="n">
-        <v>762</v>
-      </c>
-      <c r="J47" t="n">
-        <v>40</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-5.318774</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-80.663586</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>762</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2913,20 +3361,30 @@
           <t>CORONEL JOSE ANDRES RAZURI</t>
         </is>
       </c>
-      <c r="G48" t="n">
-        <v>-5.3797</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-80.6133</v>
-      </c>
-      <c r="I48" t="n">
-        <v>1362</v>
-      </c>
-      <c r="J48" t="n">
-        <v>52</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-5.3797</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-80.6133</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1362</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -2965,20 +3423,30 @@
           <t>MARIA AUXILIADORA</t>
         </is>
       </c>
-      <c r="G49" t="n">
-        <v>-5.342826</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-80.705581</v>
-      </c>
-      <c r="I49" t="n">
-        <v>575</v>
-      </c>
-      <c r="J49" t="n">
-        <v>30</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-5.342826</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>-80.705581</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>575</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -3017,20 +3485,30 @@
           <t>DIVINO MAESTRO</t>
         </is>
       </c>
-      <c r="G50" t="n">
-        <v>-5.38083</v>
-      </c>
-      <c r="H50" t="n">
-        <v>-80.694838</v>
-      </c>
-      <c r="I50" t="n">
-        <v>556</v>
-      </c>
-      <c r="J50" t="n">
-        <v>37</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-5.38083</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>-80.694838</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>556</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -3069,20 +3547,30 @@
           <t>JOSE ANTONIO ENCINAS</t>
         </is>
       </c>
-      <c r="G51" t="n">
-        <v>-5.324459</v>
-      </c>
-      <c r="H51" t="n">
-        <v>-80.781888</v>
-      </c>
-      <c r="I51" t="n">
-        <v>854</v>
-      </c>
-      <c r="J51" t="n">
-        <v>42</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-5.324459</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>-80.781888</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>854</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -3121,20 +3609,30 @@
           <t>ALEJANDRO SANCHEZ ARTEAGA</t>
         </is>
       </c>
-      <c r="G52" t="n">
-        <v>-5.3494</v>
-      </c>
-      <c r="H52" t="n">
-        <v>-80.70780000000001</v>
-      </c>
-      <c r="I52" t="n">
-        <v>965</v>
-      </c>
-      <c r="J52" t="n">
-        <v>66</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-5.3494</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>-80.7078</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>965</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -3173,20 +3671,30 @@
           <t>14063</t>
         </is>
       </c>
-      <c r="G53" t="n">
-        <v>-5.404385</v>
-      </c>
-      <c r="H53" t="n">
-        <v>-80.708613</v>
-      </c>
-      <c r="I53" t="n">
-        <v>548</v>
-      </c>
-      <c r="J53" t="n">
-        <v>27</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-5.404385</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>-80.708613</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>548</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -3225,20 +3733,30 @@
           <t>SANTA BERNARDITA</t>
         </is>
       </c>
-      <c r="G54" t="n">
-        <v>-5.40151</v>
-      </c>
-      <c r="H54" t="n">
-        <v>-80.74325</v>
-      </c>
-      <c r="I54" t="n">
-        <v>500</v>
-      </c>
-      <c r="J54" t="n">
-        <v>26</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-5.40151</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>-80.74325</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -3277,20 +3795,30 @@
           <t>14138</t>
         </is>
       </c>
-      <c r="G55" t="n">
-        <v>-4.7068</v>
-      </c>
-      <c r="H55" t="n">
-        <v>-80.1225</v>
-      </c>
-      <c r="I55" t="n">
-        <v>206</v>
-      </c>
-      <c r="J55" t="n">
-        <v>9</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-4.7068</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>-80.1225</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -3329,20 +3857,30 @@
           <t>15261</t>
         </is>
       </c>
-      <c r="G56" t="n">
-        <v>-4.7331</v>
-      </c>
-      <c r="H56" t="n">
-        <v>-80.18640000000001</v>
-      </c>
-      <c r="I56" t="n">
-        <v>355</v>
-      </c>
-      <c r="J56" t="n">
-        <v>21</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-4.7331</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>-80.1864</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -3381,20 +3919,30 @@
           <t>449</t>
         </is>
       </c>
-      <c r="G57" t="n">
-        <v>-5.009113</v>
-      </c>
-      <c r="H57" t="n">
-        <v>-80.305919</v>
-      </c>
-      <c r="I57" t="n">
-        <v>372</v>
-      </c>
-      <c r="J57" t="n">
-        <v>16</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-5.009113</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>-80.305919</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -3433,20 +3981,30 @@
           <t>14143 FELIX CARDOZA ROJAS</t>
         </is>
       </c>
-      <c r="G58" t="n">
-        <v>-4.9072</v>
-      </c>
-      <c r="H58" t="n">
-        <v>-80.208</v>
-      </c>
-      <c r="I58" t="n">
-        <v>237</v>
-      </c>
-      <c r="J58" t="n">
-        <v>13</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-4.9072</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>-80.208</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -3485,20 +4043,30 @@
           <t>15116</t>
         </is>
       </c>
-      <c r="G59" t="n">
-        <v>-5.009628</v>
-      </c>
-      <c r="H59" t="n">
-        <v>-80.305376</v>
-      </c>
-      <c r="I59" t="n">
-        <v>721</v>
-      </c>
-      <c r="J59" t="n">
-        <v>26</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0</v>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-5.009628</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>-80.305376</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>721</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -3537,20 +4105,30 @@
           <t>15262</t>
         </is>
       </c>
-      <c r="G60" t="n">
-        <v>-4.857558</v>
-      </c>
-      <c r="H60" t="n">
-        <v>-80.518443</v>
-      </c>
-      <c r="I60" t="n">
-        <v>513</v>
-      </c>
-      <c r="J60" t="n">
-        <v>28</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0</v>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-4.857558</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>-80.518443</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>513</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -3589,20 +4167,30 @@
           <t>15434 JESUS DE NAZARET / 15434 JESUS DE NAZARETH</t>
         </is>
       </c>
-      <c r="G61" t="n">
-        <v>-4.841731</v>
-      </c>
-      <c r="H61" t="n">
-        <v>-80.34309</v>
-      </c>
-      <c r="I61" t="n">
-        <v>874</v>
-      </c>
-      <c r="J61" t="n">
-        <v>51</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>-4.841731</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>-80.34309</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>874</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -3641,20 +4229,30 @@
           <t>HORACIO ZEVALLOS GAMEZ</t>
         </is>
       </c>
-      <c r="G62" t="n">
-        <v>-4.9518</v>
-      </c>
-      <c r="H62" t="n">
-        <v>-80.2508</v>
-      </c>
-      <c r="I62" t="n">
-        <v>765</v>
-      </c>
-      <c r="J62" t="n">
-        <v>45</v>
-      </c>
-      <c r="K62" t="n">
-        <v>0</v>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>-4.9518</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>-80.2508</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>765</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -3693,20 +4291,30 @@
           <t>14996</t>
         </is>
       </c>
-      <c r="G63" t="n">
-        <v>-5.038413</v>
-      </c>
-      <c r="H63" t="n">
-        <v>-80.24509500000001</v>
-      </c>
-      <c r="I63" t="n">
-        <v>298</v>
-      </c>
-      <c r="J63" t="n">
-        <v>18</v>
-      </c>
-      <c r="K63" t="n">
-        <v>0</v>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-5.038413</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>-80.245095</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -3745,20 +4353,30 @@
           <t>RICARDO PALMA</t>
         </is>
       </c>
-      <c r="G64" t="n">
-        <v>-5.40299</v>
-      </c>
-      <c r="H64" t="n">
-        <v>-80.73829000000001</v>
-      </c>
-      <c r="I64" t="n">
-        <v>76</v>
-      </c>
-      <c r="J64" t="n">
-        <v>4</v>
-      </c>
-      <c r="K64" t="n">
-        <v>0</v>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>-5.40299</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>-80.73829</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -3797,20 +4415,30 @@
           <t>LA SALLE</t>
         </is>
       </c>
-      <c r="G65" t="n">
-        <v>-5.168025</v>
-      </c>
-      <c r="H65" t="n">
-        <v>-80.632728</v>
-      </c>
-      <c r="I65" t="n">
-        <v>227</v>
-      </c>
-      <c r="J65" t="n">
-        <v>21</v>
-      </c>
-      <c r="K65" t="n">
-        <v>0</v>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>-5.168025</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>-80.632728</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -3849,20 +4477,30 @@
           <t>CRAYOLAS</t>
         </is>
       </c>
-      <c r="G66" t="n">
-        <v>-5.182321</v>
-      </c>
-      <c r="H66" t="n">
-        <v>-80.631761</v>
-      </c>
-      <c r="I66" t="n">
-        <v>31</v>
-      </c>
-      <c r="J66" t="n">
-        <v>3</v>
-      </c>
-      <c r="K66" t="n">
-        <v>3</v>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>-5.182321</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>-80.631761</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -3901,20 +4539,30 @@
           <t>MADRE DEL BUEN CONSEJO</t>
         </is>
       </c>
-      <c r="G67" t="n">
-        <v>-5.20759</v>
-      </c>
-      <c r="H67" t="n">
-        <v>-80.64592</v>
-      </c>
-      <c r="I67" t="n">
-        <v>921</v>
-      </c>
-      <c r="J67" t="n">
-        <v>50</v>
-      </c>
-      <c r="K67" t="n">
-        <v>0</v>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>-5.20759</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>-80.64592</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>921</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -3953,20 +4601,30 @@
           <t>JEAN PIAGGET</t>
         </is>
       </c>
-      <c r="G68" t="n">
-        <v>-5.18115</v>
-      </c>
-      <c r="H68" t="n">
-        <v>-80.64023</v>
-      </c>
-      <c r="I68" t="n">
-        <v>6</v>
-      </c>
-      <c r="J68" t="n">
-        <v>1</v>
-      </c>
-      <c r="K68" t="n">
-        <v>1</v>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>-5.18115</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>-80.64023</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -4005,20 +4663,30 @@
           <t>20845</t>
         </is>
       </c>
-      <c r="G69" t="n">
-        <v>-5.157299</v>
-      </c>
-      <c r="H69" t="n">
-        <v>-80.655883</v>
-      </c>
-      <c r="I69" t="n">
-        <v>298</v>
-      </c>
-      <c r="J69" t="n">
-        <v>12</v>
-      </c>
-      <c r="K69" t="n">
-        <v>0</v>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>-5.157299</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>-80.655883</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -4057,20 +4725,30 @@
           <t>PROYECTO</t>
         </is>
       </c>
-      <c r="G70" t="n">
-        <v>-5.18139</v>
-      </c>
-      <c r="H70" t="n">
-        <v>-80.62900999999999</v>
-      </c>
-      <c r="I70" t="n">
-        <v>467</v>
-      </c>
-      <c r="J70" t="n">
-        <v>25</v>
-      </c>
-      <c r="K70" t="n">
-        <v>0</v>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>-5.18139</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>-80.62901</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>467</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -4109,20 +4787,30 @@
           <t>LAS PALMAS DE PIURA</t>
         </is>
       </c>
-      <c r="G71" t="n">
-        <v>-5.17239</v>
-      </c>
-      <c r="H71" t="n">
-        <v>-80.65609000000001</v>
-      </c>
-      <c r="I71" t="n">
-        <v>370</v>
-      </c>
-      <c r="J71" t="n">
-        <v>22</v>
-      </c>
-      <c r="K71" t="n">
-        <v>0</v>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>-5.17239</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>-80.65609</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -4161,20 +4849,30 @@
           <t>PROYECTO</t>
         </is>
       </c>
-      <c r="G72" t="n">
-        <v>-5.18117</v>
-      </c>
-      <c r="H72" t="n">
-        <v>-80.62889</v>
-      </c>
-      <c r="I72" t="n">
-        <v>637</v>
-      </c>
-      <c r="J72" t="n">
-        <v>36</v>
-      </c>
-      <c r="K72" t="n">
-        <v>0</v>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>-5.18117</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>-80.62889</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>637</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
@@ -4213,20 +4911,30 @@
           <t>1330</t>
         </is>
       </c>
-      <c r="G73" t="n">
-        <v>-5.23229</v>
-      </c>
-      <c r="H73" t="n">
-        <v>-80.65834</v>
-      </c>
-      <c r="I73" t="n">
-        <v>83</v>
-      </c>
-      <c r="J73" t="n">
-        <v>3</v>
-      </c>
-      <c r="K73" t="n">
-        <v>1</v>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>-5.23229</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>-80.65834</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -4265,20 +4973,30 @@
           <t>LA SENDITA DE SANTA TERESITA DEL NIÑO JESUS</t>
         </is>
       </c>
-      <c r="G74" t="n">
-        <v>-5.19446</v>
-      </c>
-      <c r="H74" t="n">
-        <v>-80.63236000000001</v>
-      </c>
-      <c r="I74" t="n">
-        <v>6</v>
-      </c>
-      <c r="J74" t="n">
-        <v>1</v>
-      </c>
-      <c r="K74" t="n">
-        <v>1</v>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>-5.19446</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>-80.63236</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
@@ -4317,20 +5035,30 @@
           <t>LAS PRADERAS DEL NORTE</t>
         </is>
       </c>
-      <c r="G75" t="n">
-        <v>-5.18623</v>
-      </c>
-      <c r="H75" t="n">
-        <v>-80.62975</v>
-      </c>
-      <c r="I75" t="n">
-        <v>268</v>
-      </c>
-      <c r="J75" t="n">
-        <v>10</v>
-      </c>
-      <c r="K75" t="n">
-        <v>0</v>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-5.18623</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-80.62975</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -4369,20 +5097,30 @@
           <t>LUIS ANTONIO EGUIGUREN ESCUDERO</t>
         </is>
       </c>
-      <c r="G76" t="n">
-        <v>-5.17439</v>
-      </c>
-      <c r="H76" t="n">
-        <v>-80.64295</v>
-      </c>
-      <c r="I76" t="n">
-        <v>298</v>
-      </c>
-      <c r="J76" t="n">
-        <v>19</v>
-      </c>
-      <c r="K76" t="n">
-        <v>0</v>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>-5.17439</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>-80.64295</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
@@ -4421,20 +5159,30 @@
           <t>RICARDO PALMA</t>
         </is>
       </c>
-      <c r="G77" t="n">
-        <v>-5.40292</v>
-      </c>
-      <c r="H77" t="n">
-        <v>-80.7383</v>
-      </c>
-      <c r="I77" t="n">
-        <v>370</v>
-      </c>
-      <c r="J77" t="n">
-        <v>27</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0</v>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>-5.40292</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>-80.7383</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
@@ -4473,20 +5221,30 @@
           <t>SAN ANTONIO DE PADUA</t>
         </is>
       </c>
-      <c r="G78" t="n">
-        <v>-5.19186</v>
-      </c>
-      <c r="H78" t="n">
-        <v>-80.63122</v>
-      </c>
-      <c r="I78" t="n">
-        <v>57</v>
-      </c>
-      <c r="J78" t="n">
-        <v>8</v>
-      </c>
-      <c r="K78" t="n">
-        <v>1</v>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>-5.19186</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>-80.63122</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
@@ -4525,20 +5283,30 @@
           <t>SANTA MARIA ILUMINADA</t>
         </is>
       </c>
-      <c r="G79" t="n">
-        <v>-5.159393</v>
-      </c>
-      <c r="H79" t="n">
-        <v>-80.65069</v>
-      </c>
-      <c r="I79" t="n">
-        <v>481</v>
-      </c>
-      <c r="J79" t="n">
-        <v>32</v>
-      </c>
-      <c r="K79" t="n">
-        <v>0</v>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>-5.159393</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>-80.65069</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>481</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
@@ -4577,20 +5345,30 @@
           <t>INNOVA SCHOOLS - PIURA LOS EJIDOS</t>
         </is>
       </c>
-      <c r="G80" t="n">
-        <v>-5.158663</v>
-      </c>
-      <c r="H80" t="n">
-        <v>-80.627411</v>
-      </c>
-      <c r="I80" t="n">
-        <v>958</v>
-      </c>
-      <c r="J80" t="n">
-        <v>44</v>
-      </c>
-      <c r="K80" t="n">
-        <v>0</v>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>-5.158663</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>-80.627411</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>958</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -4629,20 +5407,30 @@
           <t>LA CASITA MAGICA DE LUCAS</t>
         </is>
       </c>
-      <c r="G81" t="n">
-        <v>-5.18279</v>
-      </c>
-      <c r="H81" t="n">
-        <v>-80.63938</v>
-      </c>
-      <c r="I81" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" t="n">
-        <v>0</v>
-      </c>
-      <c r="K81" t="n">
-        <v>1</v>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>-5.18279</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>-80.63938</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
@@ -4681,20 +5469,30 @@
           <t>LA GREDA NUEVA</t>
         </is>
       </c>
-      <c r="G82" t="n">
-        <v>-4.981002</v>
-      </c>
-      <c r="H82" t="n">
-        <v>-80.336781</v>
-      </c>
-      <c r="I82" t="n">
-        <v>417</v>
-      </c>
-      <c r="J82" t="n">
-        <v>17</v>
-      </c>
-      <c r="K82" t="n">
-        <v>0</v>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>-4.981002</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>-80.336781</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>417</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
@@ -4733,20 +5531,30 @@
           <t>FEDERICO VILLARREAL</t>
         </is>
       </c>
-      <c r="G83" t="n">
-        <v>-5.20061</v>
-      </c>
-      <c r="H83" t="n">
-        <v>-80.62859</v>
-      </c>
-      <c r="I83" t="n">
-        <v>2640</v>
-      </c>
-      <c r="J83" t="n">
-        <v>87</v>
-      </c>
-      <c r="K83" t="n">
-        <v>0</v>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>-5.20061</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>-80.62859</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>2640</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
@@ -4785,20 +5593,30 @@
           <t>PAMER LAS ARENAS</t>
         </is>
       </c>
-      <c r="G84" t="n">
-        <v>-5.18549</v>
-      </c>
-      <c r="H84" t="n">
-        <v>-80.62617</v>
-      </c>
-      <c r="I84" t="n">
-        <v>396</v>
-      </c>
-      <c r="J84" t="n">
-        <v>28</v>
-      </c>
-      <c r="K84" t="n">
-        <v>0</v>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>-5.18549</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>-80.62617</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>396</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
@@ -4837,20 +5655,30 @@
           <t>VILLASOL</t>
         </is>
       </c>
-      <c r="G85" t="n">
-        <v>-5.17193</v>
-      </c>
-      <c r="H85" t="n">
-        <v>-80.64448</v>
-      </c>
-      <c r="I85" t="n">
-        <v>56</v>
-      </c>
-      <c r="J85" t="n">
-        <v>7</v>
-      </c>
-      <c r="K85" t="n">
-        <v>1</v>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>-5.17193</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>-80.64448</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
@@ -4889,20 +5717,30 @@
           <t>PROYECTO WINNERS</t>
         </is>
       </c>
-      <c r="G86" t="n">
-        <v>-5.192756</v>
-      </c>
-      <c r="H86" t="n">
-        <v>-80.625051</v>
-      </c>
-      <c r="I86" t="n">
-        <v>238</v>
-      </c>
-      <c r="J86" t="n">
-        <v>19</v>
-      </c>
-      <c r="K86" t="n">
-        <v>0</v>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>-5.192756</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>-80.625051</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
@@ -4941,20 +5779,30 @@
           <t>ABC SCHOOL</t>
         </is>
       </c>
-      <c r="G87" t="n">
-        <v>-5.17234</v>
-      </c>
-      <c r="H87" t="n">
-        <v>-80.64471</v>
-      </c>
-      <c r="I87" t="n">
-        <v>0</v>
-      </c>
-      <c r="J87" t="n">
-        <v>0</v>
-      </c>
-      <c r="K87" t="n">
-        <v>1</v>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>-5.17234</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>-80.64471</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
@@ -4993,20 +5841,30 @@
           <t>MANITOS CREATIVAS SCHOOL</t>
         </is>
       </c>
-      <c r="G88" t="n">
-        <v>-5.1723</v>
-      </c>
-      <c r="H88" t="n">
-        <v>-80.6444</v>
-      </c>
-      <c r="I88" t="n">
-        <v>0</v>
-      </c>
-      <c r="J88" t="n">
-        <v>0</v>
-      </c>
-      <c r="K88" t="n">
-        <v>1</v>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>-5.1723</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>-80.6444</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
@@ -5045,20 +5903,30 @@
           <t>PROYECTO TRIUNFO IGNACIO MERINO</t>
         </is>
       </c>
-      <c r="G89" t="n">
-        <v>-5.177843</v>
-      </c>
-      <c r="H89" t="n">
-        <v>-80.646986</v>
-      </c>
-      <c r="I89" t="n">
-        <v>709</v>
-      </c>
-      <c r="J89" t="n">
-        <v>29</v>
-      </c>
-      <c r="K89" t="n">
-        <v>0</v>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>-5.177843</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>-80.646986</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>709</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
@@ -5097,20 +5965,30 @@
           <t>SANTA ROSA</t>
         </is>
       </c>
-      <c r="G90" t="n">
-        <v>-5.402155</v>
-      </c>
-      <c r="H90" t="n">
-        <v>-80.742563</v>
-      </c>
-      <c r="I90" t="n">
-        <v>268</v>
-      </c>
-      <c r="J90" t="n">
-        <v>17</v>
-      </c>
-      <c r="K90" t="n">
-        <v>0</v>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>-5.402155</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>-80.742563</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
@@ -5149,20 +6027,30 @@
           <t>PERUANO CANADIENSE DE PIURA</t>
         </is>
       </c>
-      <c r="G91" t="n">
-        <v>-5.19149</v>
-      </c>
-      <c r="H91" t="n">
-        <v>-80.62799</v>
-      </c>
-      <c r="I91" t="n">
-        <v>495</v>
-      </c>
-      <c r="J91" t="n">
-        <v>32</v>
-      </c>
-      <c r="K91" t="n">
-        <v>0</v>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>-5.19149</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>-80.62799</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
@@ -5201,20 +6089,30 @@
           <t>PAUL HARRIS</t>
         </is>
       </c>
-      <c r="G92" t="n">
-        <v>-5.18818</v>
-      </c>
-      <c r="H92" t="n">
-        <v>-80.64619</v>
-      </c>
-      <c r="I92" t="n">
-        <v>0</v>
-      </c>
-      <c r="J92" t="n">
-        <v>0</v>
-      </c>
-      <c r="K92" t="n">
-        <v>0</v>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>-5.18818</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>-80.64619</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/PIURA-PIURA-PIURA.xlsx
+++ b/ZonasEscolares/excels/PIURA-PIURA-PIURA.xlsx
@@ -501,37 +501,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>409942</t>
+          <t>411544</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>001 MARIA CONCEPCION RAMOS CAMPOS</t>
+          <t>JOSE ANTONIO ENCINAS</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-5.19929</t>
+          <t>-5.20017</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-80.63386</t>
+          <t>-80.63158</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -563,37 +563,37 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>409956</t>
+          <t>805843</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>LA CASITA MAGICA DE LUCAS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-5.18936</t>
+          <t>-5.18279</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-80.63822</t>
+          <t>-80.63938</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>410115</t>
+          <t>854975</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>ABC SCHOOL</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-5.201211</t>
+          <t>-5.17234</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-80.632621</t>
+          <t>-80.64471</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,42 +687,42 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>410238</t>
+          <t>854980</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>COMPLEJO LA ALBORADA</t>
+          <t>MANITOS CREATIVAS SCHOOL</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-5.18634</t>
+          <t>-5.1723</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-80.65428</t>
+          <t>-80.6444</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>410262</t>
+          <t>410813</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SELMIRA DE VARONA</t>
+          <t>PAUL HARRIS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-5.19173</t>
+          <t>-5.18818</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-80.64987</t>
+          <t>-80.64619</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -811,42 +811,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>410276</t>
+          <t>411657</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PNP BACILIO RAMIREZ PEÑA</t>
+          <t>LA SENDITA DE SANTA TERESITA DEL NIÑO JESUS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-5.18797</t>
+          <t>-5.19455</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-80.65006</t>
+          <t>-80.6319</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -873,42 +873,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>410281</t>
+          <t>629411</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>14001 MAGDALENA SEMINARIO DE LLIROD</t>
+          <t>JEAN PIAGGET</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-5.19625</t>
+          <t>-5.18115</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-80.6379</t>
+          <t>-80.64023</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1520</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -935,42 +935,42 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>410318</t>
+          <t>765941</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>14007</t>
+          <t>LA SENDITA DE SANTA TERESITA DEL NIÑO JESUS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-5.19012</t>
+          <t>-5.19446</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-80.65418</t>
+          <t>-80.63236</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>804</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>410375</t>
+          <t>766479</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ELVIRA CASTRO DE QUIROS</t>
+          <t>LAS PRADERAS DEL NORTE</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-5.130262</t>
+          <t>-5.18623</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-80.641116</t>
+          <t>-80.62975</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>268</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>410380</t>
+          <t>639924</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>14103 / CPED - 14103</t>
+          <t>20845</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-5.15807</t>
+          <t>-5.157299</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-80.62092</t>
+          <t>-80.655883</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>298</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>410399</t>
+          <t>409942</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SAN PEDRO</t>
+          <t>001 MARIA CONCEPCION RAMOS CAMPOS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-5.2004</t>
+          <t>-5.19929</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-80.64155</t>
+          <t>-80.63386</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1383</t>
+          <t>285</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>410422</t>
+          <t>409956</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>15005</t>
+          <t>002</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-5.2045</t>
+          <t>-5.18936</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-80.6333</t>
+          <t>-80.63822</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>279</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>410441</t>
+          <t>416080</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>VICTOR FRANCISCO ROSALES ORTEGA</t>
+          <t>14143 FELIX CARDOZA ROJAS</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-5.18607</t>
+          <t>-4.9072</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-80.63382</t>
+          <t>-80.208</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>237</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>410479</t>
+          <t>410422</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>FEDERICO HELGUERO SEMINARIO</t>
+          <t>15005</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-5.174365</t>
+          <t>-5.2045</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-80.645913</t>
+          <t>-80.6333</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>390</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,37 +1369,37 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>410525</t>
+          <t>411407</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>20001</t>
+          <t>STELLA MARIS</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-5.044701</t>
+          <t>-5.19688</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-80.693657</t>
+          <t>-80.6301</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>235</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>410554</t>
+          <t>410525</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>20436 ROSA SUAREZ RAFAEL</t>
+          <t>20001</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-5.183353</t>
+          <t>-5.044701</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-80.656988</t>
+          <t>-80.693657</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>242</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>410653</t>
+          <t>411412</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>20197</t>
+          <t>SUSANA WESLEY</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-5.20372</t>
+          <t>-5.19983</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-80.63676</t>
+          <t>-80.63765</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>449</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>410672</t>
+          <t>415684</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>PARCEMON SALDARRIAGA MONTEJO</t>
+          <t>449</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-5.18826</t>
+          <t>-5.009113</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-80.62914</t>
+          <t>-80.305919</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>372</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>410691</t>
+          <t>410771</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ANN GOULDEN</t>
+          <t>SAN MIGUEL</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-5.20277</t>
+          <t>-5.19615</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-80.62901</t>
+          <t>-80.6349</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>3429</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>163</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>410709</t>
+          <t>410380</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ROSA CARRERA DE MARTOS</t>
+          <t>14103 / CPED - 14103</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-5.18532</t>
+          <t>-5.15807</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-80.62804</t>
+          <t>-80.62092</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1062</t>
+          <t>227</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>410728</t>
+          <t>821013</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>IGNACIO MERINO</t>
+          <t>LA GREDA NUEVA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-5.17923</t>
+          <t>-4.981002</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-80.64374</t>
+          <t>-80.336781</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>417</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>410733</t>
+          <t>860293</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>IGNACIO SANCHEZ</t>
+          <t>SANTA ROSA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-5.19302</t>
+          <t>-5.402155</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-80.62747</t>
+          <t>-80.742563</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>268</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,42 +1865,42 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>410752</t>
+          <t>411006</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SAGRADO CORAZON DE JESUS</t>
+          <t>DOMENICO SAVIO</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-5.1876</t>
+          <t>-5.1819</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-80.62869</t>
+          <t>-80.63531</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1369</t>
+          <t>170</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>410771</t>
+          <t>429884</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SAN MIGUEL</t>
+          <t>14996</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-5.19615</t>
+          <t>-5.038413</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-80.6349</t>
+          <t>-80.245095</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3429</t>
+          <t>298</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>410785</t>
+          <t>766587</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CORONEL JOSE JOAQUIN INCLAN</t>
+          <t>LUIS ANTONIO EGUIGUREN ESCUDERO</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-5.19926</t>
+          <t>-5.17439</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-80.63702</t>
+          <t>-80.64295</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>298</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>410790</t>
+          <t>854150</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>ENRIQUE LOPEZ ALBUJAR</t>
+          <t>PROYECTO WINNERS</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-5.19406</t>
+          <t>-5.192756</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-80.64891</t>
+          <t>-80.625051</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1064</t>
+          <t>238</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>410827</t>
+          <t>410554</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE FATIMA</t>
+          <t>20436 ROSA SUAREZ RAFAEL</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-5.19006</t>
+          <t>-5.183353</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-80.6359</t>
+          <t>-80.656988</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1902</t>
+          <t>443</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2175,37 +2175,37 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>410846</t>
+          <t>415269</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>LOS ALGARROBOS</t>
+          <t>15261</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-5.1679</t>
+          <t>-4.7331</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-80.64952</t>
+          <t>-80.1864</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>355</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>410974</t>
+          <t>542187</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>BELEN</t>
+          <t>LA SALLE</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-5.19233</t>
+          <t>-5.168025</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-80.62737</t>
+          <t>-80.632728</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>227</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2299,37 +2299,37 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>411006</t>
+          <t>716111</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>DOMENICO SAVIO</t>
+          <t>LAS PALMAS DE PIURA</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-5.1819</t>
+          <t>-5.17239</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-80.63531</t>
+          <t>-80.65609</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>370</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>411148</t>
+          <t>410653</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>LA SEMILLITA</t>
+          <t>20197</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-5.17613</t>
+          <t>-5.20372</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-80.64111</t>
+          <t>-80.63676</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>578</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>411153</t>
+          <t>411474</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>LOS TALLANES</t>
+          <t>ADVENTISTA PIURA</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-5.18228</t>
+          <t>-5.19474</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-80.6588</t>
+          <t>-80.62961</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>386</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>411233</t>
+          <t>706051</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LOURDES</t>
+          <t>PROYECTO</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-5.1928</t>
+          <t>-5.18139</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-80.63403</t>
+          <t>-80.62901</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1031</t>
+          <t>467</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>411327</t>
+          <t>411153</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>SAN LUIS GONZAGA</t>
+          <t>LOS TALLANES</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-5.181578</t>
+          <t>-5.18228</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-80.633864</t>
+          <t>-80.6588</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>266</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>411389</t>
+          <t>414905</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>SANTA MARIA</t>
+          <t>SANTA BERNARDITA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-5.184422</t>
+          <t>-5.40151</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-80.62765</t>
+          <t>-80.74325</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>847</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2671,37 +2671,37 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>411407</t>
+          <t>416396</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>STELLA MARIS</t>
+          <t>15116</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-5.19688</t>
+          <t>-5.009628</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-80.6301</t>
+          <t>-80.305376</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>721</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>411412</t>
+          <t>411148</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>SUSANA WESLEY</t>
+          <t>LA SEMILLITA</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-5.19983</t>
+          <t>-5.17613</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-80.63765</t>
+          <t>-80.64111</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>449</t>
+          <t>442</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>411426</t>
+          <t>414689</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>TURICARA</t>
+          <t>14063</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-5.169126</t>
+          <t>-5.404385</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-80.635489</t>
+          <t>-80.708613</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>548</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>411474</t>
+          <t>770202</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>ADVENTISTA PIURA</t>
+          <t>RICARDO PALMA</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-5.19474</t>
+          <t>-5.40292</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-80.62961</t>
+          <t>-80.7383</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>370</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>411520</t>
+          <t>416565</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>HOGAR SAN ANTONIO</t>
+          <t>15262</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-5.191628</t>
+          <t>-4.857558</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-80.634409</t>
+          <t>-80.518443</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>513</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,37 +2981,37 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>411544</t>
+          <t>829721</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>JOSE ANTONIO ENCINAS</t>
+          <t>PAMER LAS ARENAS</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-5.20017</t>
+          <t>-5.18549</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-80.63158</t>
+          <t>-80.62617</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>396</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>411558</t>
+          <t>860274</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>VALLESOL</t>
+          <t>PROYECTO TRIUNFO IGNACIO MERINO</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-5.17874</t>
+          <t>-5.177843</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-80.6327</t>
+          <t>-80.646986</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1018</t>
+          <t>709</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3105,42 +3105,42 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>411596</t>
+          <t>545143</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>MARIA MONTESSORI</t>
+          <t>CRAYOLAS</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-5.17481</t>
+          <t>-5.182321</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-80.6284</t>
+          <t>-80.631761</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>875</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>411657</t>
+          <t>765535</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>LA SENDITA DE SANTA TERESITA DEL NIÑO JESUS</t>
+          <t>1330</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-5.19455</t>
+          <t>-5.23229</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-80.6319</t>
+          <t>-80.65834</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>83</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>413618</t>
+          <t>410375</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>JOSE CARLOS MARIATEGUI LACHIRA</t>
+          <t>ELVIRA CASTRO DE QUIROS</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-5.280572</t>
+          <t>-5.130262</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-80.714728</t>
+          <t>-80.641116</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>499</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>413939</t>
+          <t>414222</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>FEDERICO VILLARREAL</t>
+          <t>MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-5.318774</t>
+          <t>-5.342826</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-80.663586</t>
+          <t>-80.705581</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>575</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>413944</t>
+          <t>410733</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CORONEL JOSE ANDRES RAZURI</t>
+          <t>IGNACIO SANCHEZ</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-5.3797</t>
+          <t>-5.19302</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-80.6133</t>
+          <t>-80.62747</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1362</t>
+          <t>812</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>414222</t>
+          <t>776299</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>MARIA AUXILIADORA</t>
+          <t>SANTA MARIA ILUMINADA</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-5.342826</t>
+          <t>-5.159393</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-80.705581</t>
+          <t>-80.65069</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>481</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>414241</t>
+          <t>864719</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>DIVINO MAESTRO</t>
+          <t>PERUANO CANADIENSE DE PIURA</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-5.38083</t>
+          <t>-5.19149</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-80.694838</t>
+          <t>-80.62799</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>556</t>
+          <t>495</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>414397</t>
+          <t>410238</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>JOSE ANTONIO ENCINAS</t>
+          <t>COMPLEJO LA ALBORADA</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-5.324459</t>
+          <t>-5.18634</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-80.781888</t>
+          <t>-80.65428</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>658</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3601,32 +3601,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>414458</t>
+          <t>410318</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>ALEJANDRO SANCHEZ ARTEAGA</t>
+          <t>14007</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-5.3494</t>
+          <t>-5.19012</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-80.7078</t>
+          <t>-80.65418</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>965</t>
+          <t>804</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3663,32 +3663,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>414689</t>
+          <t>411327</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>14063</t>
+          <t>SAN LUIS GONZAGA</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-5.404385</t>
+          <t>-5.181578</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-80.708613</t>
+          <t>-80.633864</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>318</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3725,32 +3725,32 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>414905</t>
+          <t>410672</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SANTA BERNARDITA</t>
+          <t>PARCEMON SALDARRIAGA MONTEJO</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-5.40151</t>
+          <t>-5.18826</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-80.74325</t>
+          <t>-80.62914</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>890</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3787,32 +3787,32 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>415170</t>
+          <t>749630</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>14138</t>
+          <t>PROYECTO</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-4.7068</t>
+          <t>-5.18117</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-80.1225</t>
+          <t>-80.62889</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>637</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3849,37 +3849,37 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>415269</t>
+          <t>410846</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>15261</t>
+          <t>LOS ALGARROBOS</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-4.7331</t>
+          <t>-5.1679</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-80.1864</t>
+          <t>-80.64952</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>714</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3911,32 +3911,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>415684</t>
+          <t>413618</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>449</t>
+          <t>JOSE CARLOS MARIATEGUI LACHIRA</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-5.009113</t>
+          <t>-5.280572</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-80.305919</t>
+          <t>-80.714728</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>551</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3973,32 +3973,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>416080</t>
+          <t>414241</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>14143 FELIX CARDOZA ROJAS</t>
+          <t>DIVINO MAESTRO</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-4.9072</t>
+          <t>-5.38083</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-80.208</t>
+          <t>-80.694838</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>556</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4035,32 +4035,32 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>416396</t>
+          <t>410262</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>15116</t>
+          <t>SELMIRA DE VARONA</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-5.009628</t>
+          <t>-5.19173</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-80.305376</t>
+          <t>-80.64987</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>934</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4097,37 +4097,37 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>416565</t>
+          <t>410115</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>15262</t>
+          <t>225</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-4.857558</t>
+          <t>-5.201211</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-80.518443</t>
+          <t>-80.632621</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>78</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4159,32 +4159,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>416754</t>
+          <t>530066</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>15434 JESUS DE NAZARET / 15434 JESUS DE NAZARETH</t>
+          <t>RICARDO PALMA</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-4.841731</t>
+          <t>-5.40299</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-80.34309</t>
+          <t>-80.73829</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>76</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4221,32 +4221,32 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>417112</t>
+          <t>410276</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>HORACIO ZEVALLOS GAMEZ</t>
+          <t>PNP BACILIO RAMIREZ PEÑA</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-4.9518</t>
+          <t>-5.18797</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>-80.2508</t>
+          <t>-80.65006</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>860</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4283,32 +4283,32 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>429884</t>
+          <t>410691</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>14996</t>
+          <t>ANN GOULDEN</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-5.038413</t>
+          <t>-5.20277</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>-80.245095</t>
+          <t>-80.62901</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4345,32 +4345,32 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>530066</t>
+          <t>413939</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>RICARDO PALMA</t>
+          <t>FEDERICO VILLARREAL</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-5.40299</t>
+          <t>-5.318774</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>-80.73829</t>
+          <t>-80.663586</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>762</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4407,32 +4407,32 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>542187</t>
+          <t>410709</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>LA SALLE</t>
+          <t>ROSA CARRERA DE MARTOS</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-5.168025</t>
+          <t>-5.18532</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>-80.632728</t>
+          <t>-80.62804</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>1062</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4469,37 +4469,37 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>545143</t>
+          <t>411520</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>CRAYOLAS</t>
+          <t>HOGAR SAN ANTONIO</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-5.182321</t>
+          <t>-5.191628</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>-80.631761</t>
+          <t>-80.634409</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>630</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4531,32 +4531,32 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>613518</t>
+          <t>414397</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>MADRE DEL BUEN CONSEJO</t>
+          <t>JOSE ANTONIO ENCINAS</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-5.20759</t>
+          <t>-5.324459</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>-80.64592</t>
+          <t>-80.781888</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>854</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4593,42 +4593,42 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>629411</t>
+          <t>410785</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>JEAN PIAGGET</t>
+          <t>CORONEL JOSE JOAQUIN INCLAN</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-5.18115</t>
+          <t>-5.19926</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>-80.64023</t>
+          <t>-80.63702</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1080</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4655,32 +4655,32 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>639924</t>
+          <t>781663</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>20845</t>
+          <t>INNOVA SCHOOLS - PIURA LOS EJIDOS</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-5.157299</t>
+          <t>-5.158663</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>-80.655883</t>
+          <t>-80.627411</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>958</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4717,32 +4717,32 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>706051</t>
+          <t>411389</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>PROYECTO</t>
+          <t>SANTA MARIA</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-5.18139</t>
+          <t>-5.184422</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>-80.62901</t>
+          <t>-80.62765</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>467</t>
+          <t>847</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4779,32 +4779,32 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>716111</t>
+          <t>417112</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>LAS PALMAS DE PIURA</t>
+          <t>HORACIO ZEVALLOS GAMEZ</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-5.17239</t>
+          <t>-4.9518</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>-80.65609</t>
+          <t>-80.2508</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>765</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4841,32 +4841,32 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>749630</t>
+          <t>410441</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>PROYECTO</t>
+          <t>VICTOR FRANCISCO ROSALES ORTEGA</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-5.18117</t>
+          <t>-5.18607</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>-80.62889</t>
+          <t>-80.63382</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4903,42 +4903,42 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>765535</t>
+          <t>410974</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>1330</t>
+          <t>BELEN</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-5.23229</t>
+          <t>-5.19233</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>-80.65834</t>
+          <t>-80.62737</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>982</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4965,37 +4965,37 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>765941</t>
+          <t>613518</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>LA SENDITA DE SANTA TERESITA DEL NIÑO JESUS</t>
+          <t>MADRE DEL BUEN CONSEJO</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-5.19446</t>
+          <t>-5.20759</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>-80.63236</t>
+          <t>-80.64592</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>921</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5027,32 +5027,32 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>766479</t>
+          <t>410728</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>LAS PRADERAS DEL NORTE</t>
+          <t>IGNACIO MERINO</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-5.18623</t>
+          <t>-5.17923</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>-80.62975</t>
+          <t>-80.64374</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>51</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5089,32 +5089,32 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>766587</t>
+          <t>411426</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>LUIS ANTONIO EGUIGUREN ESCUDERO</t>
+          <t>TURICARA</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-5.17439</t>
+          <t>-5.169126</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>-80.64295</t>
+          <t>-80.635489</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>621</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>51</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5151,32 +5151,32 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>770202</t>
+          <t>416754</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>RICARDO PALMA</t>
+          <t>15434 JESUS DE NAZARET / 15434 JESUS DE NAZARETH</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-5.40292</t>
+          <t>-4.841731</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>-80.7383</t>
+          <t>-80.34309</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>874</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>51</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5213,42 +5213,42 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>775916</t>
+          <t>413944</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>SAN ANTONIO DE PADUA</t>
+          <t>CORONEL JOSE ANDRES RAZURI</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-5.19186</t>
+          <t>-5.3797</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>-80.63122</t>
+          <t>-80.6133</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>1362</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>52</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5275,32 +5275,32 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>776299</t>
+          <t>410752</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>SANTA MARIA ILUMINADA</t>
+          <t>SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-5.159393</t>
+          <t>-5.1876</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>-80.65069</t>
+          <t>-80.62869</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>1369</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5337,32 +5337,32 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>781663</t>
+          <t>410479</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS - PIURA LOS EJIDOS</t>
+          <t>FEDERICO HELGUERO SEMINARIO</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-5.158663</t>
+          <t>-5.174365</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>-80.627411</t>
+          <t>-80.645913</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>1355</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>57</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5399,42 +5399,42 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>805843</t>
+          <t>411596</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>LA CASITA MAGICA DE LUCAS</t>
+          <t>MARIA MONTESSORI</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-5.18279</t>
+          <t>-5.17481</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>-80.63938</t>
+          <t>-80.6284</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>875</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5461,32 +5461,32 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>821013</t>
+          <t>411233</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>LA GREDA NUEVA</t>
+          <t>NUESTRA SEÑORA DE LOURDES</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-4.981002</t>
+          <t>-5.1928</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>-80.336781</t>
+          <t>-80.63403</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>417</t>
+          <t>1031</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>61</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5523,32 +5523,32 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>828646</t>
+          <t>410281</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>FEDERICO VILLARREAL</t>
+          <t>14001 MAGDALENA SEMINARIO DE LLIROD</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-5.20061</t>
+          <t>-5.19625</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>-80.62859</t>
+          <t>-80.6379</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>62</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5585,32 +5585,32 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>829721</t>
+          <t>410399</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>PAMER LAS ARENAS</t>
+          <t>SAN PEDRO</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-5.18549</t>
+          <t>-5.2004</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>-80.62617</t>
+          <t>-80.64155</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>1383</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>65</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5647,37 +5647,37 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>833638</t>
+          <t>414458</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>VILLASOL</t>
+          <t>ALEJANDRO SANCHEZ ARTEAGA</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-5.17193</t>
+          <t>-5.3494</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>-80.64448</t>
+          <t>-80.7078</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>965</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>66</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5709,32 +5709,32 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>854150</t>
+          <t>411558</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>PROYECTO WINNERS</t>
+          <t>VALLESOL</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>-5.192756</t>
+          <t>-5.17874</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>-80.625051</t>
+          <t>-80.6327</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>67</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5771,42 +5771,42 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>854975</t>
+          <t>410790</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>ABC SCHOOL</t>
+          <t>ENRIQUE LOPEZ ALBUJAR</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-5.17234</t>
+          <t>-5.19406</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>-80.64471</t>
+          <t>-80.64891</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1064</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>69</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5833,32 +5833,32 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>854980</t>
+          <t>833638</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>MANITOS CREATIVAS SCHOOL</t>
+          <t>VILLASOL</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>-5.1723</t>
+          <t>-5.17193</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>-80.6444</t>
+          <t>-80.64448</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5895,32 +5895,32 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>860274</t>
+          <t>410827</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>PROYECTO TRIUNFO IGNACIO MERINO</t>
+          <t>NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>-5.177843</t>
+          <t>-5.19006</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>-80.646986</t>
+          <t>-80.6359</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>1902</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>79</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5957,42 +5957,42 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>860293</t>
+          <t>775916</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>SANTA ROSA</t>
+          <t>SAN ANTONIO DE PADUA</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>-5.402155</t>
+          <t>-5.19186</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>-80.742563</t>
+          <t>-80.63122</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>57</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6019,32 +6019,32 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>864719</t>
+          <t>828646</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>PERUANO CANADIENSE DE PIURA</t>
+          <t>FEDERICO VILLARREAL</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>-5.19149</t>
+          <t>-5.20061</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>-80.62799</t>
+          <t>-80.62859</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>87</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6081,32 +6081,32 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>410813</t>
+          <t>415170</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>PAUL HARRIS</t>
+          <t>14138</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>-5.18818</t>
+          <t>-4.7068</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>-80.64619</t>
+          <t>-80.1225</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>206</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/PIURA-PIURA-PIURA.xlsx
+++ b/ZonasEscolares/excels/PIURA-PIURA-PIURA.xlsx
@@ -501,37 +501,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>411544</t>
+          <t>864719</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>JOSE ANTONIO ENCINAS</t>
+          <t>PERUANO CANADIENSE DE PIURA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-5.20017</t>
+          <t>495</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-80.63158</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5.19149</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-80.62799</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -563,37 +563,37 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>805843</t>
+          <t>860293</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>LA CASITA MAGICA DE LUCAS</t>
+          <t>SANTA ROSA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-5.18279</t>
+          <t>268</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-80.63938</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5.402155</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-80.742563</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,37 +625,37 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>854975</t>
+          <t>860274</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ABC SCHOOL</t>
+          <t>PROYECTO TRIUNFO IGNACIO MERINO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-5.17234</t>
+          <t>709</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-80.64471</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5.177843</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-80.646986</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -697,22 +697,22 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>-5.1723</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>-80.6444</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,42 +749,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>410813</t>
+          <t>854975</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>PAUL HARRIS</t>
+          <t>ABC SCHOOL</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-5.18818</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-80.64619</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5.17234</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-80.64471</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -811,37 +811,37 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>411657</t>
+          <t>854150</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>LA SENDITA DE SANTA TERESITA DEL NIÑO JESUS</t>
+          <t>PROYECTO WINNERS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-5.19455</t>
+          <t>238</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-80.6319</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-5.192756</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-80.625051</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>629411</t>
+          <t>833638</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JEAN PIAGGET</t>
+          <t>VILLASOL</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-5.18115</t>
+          <t>56</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-80.64023</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>-5.17193</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-80.64448</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,37 +935,37 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>765941</t>
+          <t>829721</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>LA SENDITA DE SANTA TERESITA DEL NIÑO JESUS</t>
+          <t>PAMER LAS ARENAS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-5.19446</t>
+          <t>396</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-80.63236</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>-5.18549</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-80.62617</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>766479</t>
+          <t>828646</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>LAS PRADERAS DEL NORTE</t>
+          <t>FEDERICO VILLARREAL</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-5.18623</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-80.62975</t>
+          <t>87</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>-5.20061</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-80.62859</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>639924</t>
+          <t>821013</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>20845</t>
+          <t>LA GREDA NUEVA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-5.157299</t>
+          <t>417</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-80.655883</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>-4.981002</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-80.336781</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,37 +1121,37 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>409942</t>
+          <t>805843</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>001 MARIA CONCEPCION RAMOS CAMPOS</t>
+          <t>LA CASITA MAGICA DE LUCAS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-5.19929</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-80.63386</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>-5.18279</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-80.63938</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>409956</t>
+          <t>781663</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>INNOVA SCHOOLS - PIURA LOS EJIDOS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-5.18936</t>
+          <t>958</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-80.63822</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>-5.158663</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-80.627411</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>416080</t>
+          <t>776299</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>14143 FELIX CARDOZA ROJAS</t>
+          <t>SANTA MARIA ILUMINADA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-4.9072</t>
+          <t>481</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-80.208</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>-5.159393</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-80.65069</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,37 +1307,37 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>410422</t>
+          <t>775916</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>15005</t>
+          <t>SAN ANTONIO DE PADUA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-5.2045</t>
+          <t>57</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-80.6333</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>-5.19186</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-80.63122</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1369,37 +1369,37 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>411407</t>
+          <t>770202</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>STELLA MARIS</t>
+          <t>RICARDO PALMA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-5.19688</t>
+          <t>370</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-80.6301</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>-5.40292</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-80.7383</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>410525</t>
+          <t>766587</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>20001</t>
+          <t>LUIS ANTONIO EGUIGUREN ESCUDERO</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-5.044701</t>
+          <t>298</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-80.693657</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>-5.17439</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-80.64295</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>411412</t>
+          <t>766479</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SUSANA WESLEY</t>
+          <t>LAS PRADERAS DEL NORTE</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-5.19983</t>
+          <t>268</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-80.63765</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>449</t>
+          <t>-5.18623</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-80.62975</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1555,37 +1555,37 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>415684</t>
+          <t>765941</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>449</t>
+          <t>LA SENDITA DE SANTA TERESITA DEL NIÑO JESUS</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-5.009113</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-80.305919</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>-5.19446</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-80.63236</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1617,42 +1617,42 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>410771</t>
+          <t>765535</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SAN MIGUEL</t>
+          <t>1330</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-5.19615</t>
+          <t>83</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-80.6349</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3429</t>
+          <t>-5.23229</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>-80.65834</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>410380</t>
+          <t>749630</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>14103 / CPED - 14103</t>
+          <t>PROYECTO</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-5.15807</t>
+          <t>637</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-80.62092</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>-5.18117</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-80.62889</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>821013</t>
+          <t>716111</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>LA GREDA NUEVA</t>
+          <t>LAS PALMAS DE PIURA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-4.981002</t>
+          <t>370</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-80.336781</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>417</t>
+          <t>-5.17239</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-80.65609</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>860293</t>
+          <t>706051</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SANTA ROSA</t>
+          <t>PROYECTO</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-5.402155</t>
+          <t>467</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-80.742563</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>-5.18139</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-80.62901</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,42 +1865,42 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>411006</t>
+          <t>639924</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>DOMENICO SAVIO</t>
+          <t>20845</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-5.1819</t>
+          <t>298</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-80.63531</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>-5.157299</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-80.655883</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1927,37 +1927,37 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>429884</t>
+          <t>629411</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>14996</t>
+          <t>JEAN PIAGGET</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-5.038413</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-80.245095</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>-5.18115</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-80.64023</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>766587</t>
+          <t>613518</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>LUIS ANTONIO EGUIGUREN ESCUDERO</t>
+          <t>MADRE DEL BUEN CONSEJO</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-5.17439</t>
+          <t>921</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-80.64295</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>-5.20759</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-80.64592</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,37 +2051,37 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>854150</t>
+          <t>545143</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>PROYECTO WINNERS</t>
+          <t>CRAYOLAS</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-5.192756</t>
+          <t>31</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-80.625051</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>-5.182321</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-80.631761</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>410554</t>
+          <t>542187</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>20436 ROSA SUAREZ RAFAEL</t>
+          <t>LA SALLE</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-5.183353</t>
+          <t>227</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-80.656988</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>-5.168025</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-80.632728</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>415269</t>
+          <t>530066</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>15261</t>
+          <t>RICARDO PALMA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-4.7331</t>
+          <t>76</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-80.1864</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>-5.40299</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-80.73829</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>542187</t>
+          <t>429884</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>LA SALLE</t>
+          <t>14996</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-5.168025</t>
+          <t>298</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-80.632728</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>-5.038413</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-80.245095</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>716111</t>
+          <t>417112</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>LAS PALMAS DE PIURA</t>
+          <t>HORACIO ZEVALLOS GAMEZ</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-5.17239</t>
+          <t>765</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-80.65609</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>-4.9518</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-80.2508</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>410653</t>
+          <t>416754</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>20197</t>
+          <t>15434 JESUS DE NAZARET / 15434 JESUS DE NAZARETH</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-5.20372</t>
+          <t>874</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-80.63676</t>
+          <t>51</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>-4.841731</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-80.34309</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>411474</t>
+          <t>416565</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ADVENTISTA PIURA</t>
+          <t>15262</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-5.19474</t>
+          <t>513</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-80.62961</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>-4.857558</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-80.518443</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>706051</t>
+          <t>416396</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>PROYECTO</t>
+          <t>15116</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-5.18139</t>
+          <t>721</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-80.62901</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>467</t>
+          <t>-5.009628</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-80.305376</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>411153</t>
+          <t>416080</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>LOS TALLANES</t>
+          <t>14143 FELIX CARDOZA ROJAS</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-5.18228</t>
+          <t>237</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-80.6588</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>-4.9072</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-80.208</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>414905</t>
+          <t>415684</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>SANTA BERNARDITA</t>
+          <t>449</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-5.40151</t>
+          <t>372</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-80.74325</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>-5.009113</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-80.305919</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>416396</t>
+          <t>415269</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>15116</t>
+          <t>15261</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-5.009628</t>
+          <t>355</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-80.305376</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>-4.7331</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-80.1864</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>411148</t>
+          <t>415170</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>LA SEMILLITA</t>
+          <t>14138</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-5.17613</t>
+          <t>206</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-80.64111</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>-4.7068</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-80.1225</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>414689</t>
+          <t>414905</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>14063</t>
+          <t>SANTA BERNARDITA</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-5.404385</t>
+          <t>500</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-80.708613</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>-5.40151</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-80.74325</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>770202</t>
+          <t>414689</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>RICARDO PALMA</t>
+          <t>14063</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-5.40292</t>
+          <t>548</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-80.7383</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>-5.404385</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-80.708613</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>416565</t>
+          <t>414458</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>15262</t>
+          <t>ALEJANDRO SANCHEZ ARTEAGA</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-4.857558</t>
+          <t>965</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-80.518443</t>
+          <t>66</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>-5.3494</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-80.7078</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>829721</t>
+          <t>414397</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>PAMER LAS ARENAS</t>
+          <t>JOSE ANTONIO ENCINAS</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-5.18549</t>
+          <t>854</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-80.62617</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>-5.324459</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-80.781888</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>860274</t>
+          <t>414241</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>PROYECTO TRIUNFO IGNACIO MERINO</t>
+          <t>DIVINO MAESTRO</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-5.177843</t>
+          <t>556</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-80.646986</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>-5.38083</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-80.694838</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3105,37 +3105,37 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>545143</t>
+          <t>414222</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>CRAYOLAS</t>
+          <t>MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-5.182321</t>
+          <t>575</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-80.631761</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-5.342826</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-80.705581</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3167,37 +3167,37 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>765535</t>
+          <t>413944</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1330</t>
+          <t>CORONEL JOSE ANDRES RAZURI</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-5.23229</t>
+          <t>1362</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-80.65834</t>
+          <t>52</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>-5.3797</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-80.6133</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>410375</t>
+          <t>413939</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>ELVIRA CASTRO DE QUIROS</t>
+          <t>FEDERICO VILLARREAL</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-5.130262</t>
+          <t>762</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-80.641116</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>-5.318774</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-80.663586</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>414222</t>
+          <t>413618</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>MARIA AUXILIADORA</t>
+          <t>JOSE CARLOS MARIATEGUI LACHIRA</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-5.342826</t>
+          <t>551</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-80.705581</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>-5.280572</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-80.714728</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3353,37 +3353,37 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>410733</t>
+          <t>411657</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>IGNACIO SANCHEZ</t>
+          <t>LA SENDITA DE SANTA TERESITA DEL NIÑO JESUS</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-5.19302</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-80.62747</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>-5.19455</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-80.6319</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>776299</t>
+          <t>411596</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>SANTA MARIA ILUMINADA</t>
+          <t>MARIA MONTESSORI</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-5.159393</t>
+          <t>875</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-80.65069</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>-5.17481</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-80.6284</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>864719</t>
+          <t>411558</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>PERUANO CANADIENSE DE PIURA</t>
+          <t>VALLESOL</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-5.19149</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-80.62799</t>
+          <t>67</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>-5.17874</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-80.6327</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3539,42 +3539,42 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>410238</t>
+          <t>411544</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>COMPLEJO LA ALBORADA</t>
+          <t>JOSE ANTONIO ENCINAS</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-5.18634</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-80.65428</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>-5.20017</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-80.63158</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3601,32 +3601,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>410318</t>
+          <t>411520</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>14007</t>
+          <t>HOGAR SAN ANTONIO</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-5.19012</t>
+          <t>630</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-80.65418</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>804</t>
+          <t>-5.191628</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-80.634409</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3663,32 +3663,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>411327</t>
+          <t>411474</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>SAN LUIS GONZAGA</t>
+          <t>ADVENTISTA PIURA</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-5.181578</t>
+          <t>386</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-80.633864</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>-5.19474</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-80.62961</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3725,32 +3725,32 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>410672</t>
+          <t>411426</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>PARCEMON SALDARRIAGA MONTEJO</t>
+          <t>TURICARA</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-5.18826</t>
+          <t>621</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-80.62914</t>
+          <t>51</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>-5.169126</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>-80.635489</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3787,32 +3787,32 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>749630</t>
+          <t>411412</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>PROYECTO</t>
+          <t>SUSANA WESLEY</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-5.18117</t>
+          <t>449</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-80.62889</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>-5.19983</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-80.63765</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3849,32 +3849,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>410846</t>
+          <t>411407</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>LOS ALGARROBOS</t>
+          <t>STELLA MARIS</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-5.1679</t>
+          <t>235</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-80.64952</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>-5.19688</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-80.6301</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3911,32 +3911,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>413618</t>
+          <t>411389</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>JOSE CARLOS MARIATEGUI LACHIRA</t>
+          <t>SANTA MARIA</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-5.280572</t>
+          <t>847</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-80.714728</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>-5.184422</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-80.62765</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3973,32 +3973,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>414241</t>
+          <t>411327</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>DIVINO MAESTRO</t>
+          <t>SAN LUIS GONZAGA</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-5.38083</t>
+          <t>318</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-80.694838</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>556</t>
+          <t>-5.181578</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-80.633864</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4035,32 +4035,32 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>410262</t>
+          <t>411233</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>SELMIRA DE VARONA</t>
+          <t>NUESTRA SEÑORA DE LOURDES</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-5.19173</t>
+          <t>1031</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-80.64987</t>
+          <t>61</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>-5.1928</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-80.63403</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4097,37 +4097,37 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>410115</t>
+          <t>411153</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>LOS TALLANES</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-5.201211</t>
+          <t>266</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-80.632621</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>-5.18228</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-80.6588</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4159,32 +4159,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>530066</t>
+          <t>411148</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>RICARDO PALMA</t>
+          <t>LA SEMILLITA</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-5.40299</t>
+          <t>442</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-80.73829</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>-5.17613</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-80.64111</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4221,37 +4221,37 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>410276</t>
+          <t>411006</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>PNP BACILIO RAMIREZ PEÑA</t>
+          <t>DOMENICO SAVIO</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-5.18797</t>
+          <t>170</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>-80.65006</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>-5.1819</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>-80.63531</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>410691</t>
+          <t>410974</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>ANN GOULDEN</t>
+          <t>BELEN</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-5.20277</t>
+          <t>982</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>-80.62901</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>-5.19233</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>-80.62737</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4345,37 +4345,37 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>413939</t>
+          <t>410846</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>FEDERICO VILLARREAL</t>
+          <t>LOS ALGARROBOS</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-5.318774</t>
+          <t>714</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>-80.663586</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>-5.1679</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>-80.64952</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4407,32 +4407,32 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>410709</t>
+          <t>410827</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>ROSA CARRERA DE MARTOS</t>
+          <t>NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-5.18532</t>
+          <t>1902</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>-80.62804</t>
+          <t>79</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>1062</t>
+          <t>-5.19006</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>-80.6359</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4469,32 +4469,32 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>411520</t>
+          <t>410813</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>HOGAR SAN ANTONIO</t>
+          <t>PAUL HARRIS</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-5.191628</t>
+          <t>68</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>-80.634409</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>-5.18818</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>-80.64619</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4531,32 +4531,32 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>414397</t>
+          <t>410790</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>JOSE ANTONIO ENCINAS</t>
+          <t>ENRIQUE LOPEZ ALBUJAR</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-5.324459</t>
+          <t>1064</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>-80.781888</t>
+          <t>69</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>-5.19406</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>-80.64891</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4603,22 +4603,22 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
           <t>-5.19926</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t>-80.63702</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>43</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4655,32 +4655,32 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>781663</t>
+          <t>410771</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS - PIURA LOS EJIDOS</t>
+          <t>SAN MIGUEL</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-5.158663</t>
+          <t>3429</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>-80.627411</t>
+          <t>163</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>-5.19615</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>-80.6349</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4717,32 +4717,32 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>411389</t>
+          <t>410752</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>SANTA MARIA</t>
+          <t>SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-5.184422</t>
+          <t>1369</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>-80.62765</t>
+          <t>56</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>847</t>
+          <t>-5.1876</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>-80.62869</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4779,32 +4779,32 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>417112</t>
+          <t>410733</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>HORACIO ZEVALLOS GAMEZ</t>
+          <t>IGNACIO SANCHEZ</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-4.9518</t>
+          <t>812</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>-80.2508</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>-5.19302</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>-80.62747</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4841,32 +4841,32 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>410441</t>
+          <t>410728</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>VICTOR FRANCISCO ROSALES ORTEGA</t>
+          <t>IGNACIO MERINO</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-5.18607</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>-80.63382</t>
+          <t>51</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>-5.17923</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>-80.64374</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4903,32 +4903,32 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>410974</t>
+          <t>410709</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>BELEN</t>
+          <t>ROSA CARRERA DE MARTOS</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-5.19233</t>
+          <t>1062</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>-80.62737</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>-5.18532</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>-80.62804</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4965,32 +4965,32 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>613518</t>
+          <t>410691</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>MADRE DEL BUEN CONSEJO</t>
+          <t>ANN GOULDEN</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-5.20759</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>-80.64592</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>-5.20277</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>-80.62901</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5027,32 +5027,32 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>410728</t>
+          <t>410672</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>IGNACIO MERINO</t>
+          <t>PARCEMON SALDARRIAGA MONTEJO</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-5.17923</t>
+          <t>890</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>-80.64374</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>-5.18826</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>-80.62914</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5089,32 +5089,32 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>411426</t>
+          <t>410653</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>TURICARA</t>
+          <t>20197</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-5.169126</t>
+          <t>578</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>-80.635489</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>-5.20372</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>-80.63676</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5151,32 +5151,32 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>416754</t>
+          <t>410554</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>15434 JESUS DE NAZARET / 15434 JESUS DE NAZARETH</t>
+          <t>20436 ROSA SUAREZ RAFAEL</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-4.841731</t>
+          <t>443</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>-80.34309</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>-5.183353</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>-80.656988</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5213,32 +5213,32 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>413944</t>
+          <t>410525</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>CORONEL JOSE ANDRES RAZURI</t>
+          <t>20001</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-5.3797</t>
+          <t>242</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>-80.6133</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>1362</t>
+          <t>-5.044701</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>-80.693657</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5275,32 +5275,32 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>410752</t>
+          <t>410479</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>SAGRADO CORAZON DE JESUS</t>
+          <t>FEDERICO HELGUERO SEMINARIO</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-5.1876</t>
+          <t>1355</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>-80.62869</t>
+          <t>57</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>1369</t>
+          <t>-5.174365</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>-80.645913</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5337,32 +5337,32 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>410479</t>
+          <t>410441</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>FEDERICO HELGUERO SEMINARIO</t>
+          <t>VICTOR FRANCISCO ROSALES ORTEGA</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-5.174365</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>-80.645913</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>-5.18607</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>-80.63382</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5399,32 +5399,32 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>411596</t>
+          <t>410422</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>MARIA MONTESSORI</t>
+          <t>15005</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-5.17481</t>
+          <t>390</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>-80.6284</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>875</t>
+          <t>-5.2045</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>-80.6333</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -5461,32 +5461,32 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>411233</t>
+          <t>410399</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LOURDES</t>
+          <t>SAN PEDRO</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-5.1928</t>
+          <t>1383</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>-80.63403</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>1031</t>
+          <t>-5.2004</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>-80.64155</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5523,32 +5523,32 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>410281</t>
+          <t>410380</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>14001 MAGDALENA SEMINARIO DE LLIROD</t>
+          <t>14103 / CPED - 14103</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-5.19625</t>
+          <t>227</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>-80.6379</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>1520</t>
+          <t>-5.15807</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>-80.62092</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5585,32 +5585,32 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>410399</t>
+          <t>410375</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>SAN PEDRO</t>
+          <t>ELVIRA CASTRO DE QUIROS</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-5.2004</t>
+          <t>499</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>-80.64155</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>1383</t>
+          <t>-5.130262</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>-80.641116</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5647,32 +5647,32 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>414458</t>
+          <t>410318</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>ALEJANDRO SANCHEZ ARTEAGA</t>
+          <t>14007</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-5.3494</t>
+          <t>804</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>-80.7078</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>965</t>
+          <t>-5.19012</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>-80.65418</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5682,7 +5682,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5709,32 +5709,32 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>411558</t>
+          <t>410281</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>VALLESOL</t>
+          <t>14001 MAGDALENA SEMINARIO DE LLIROD</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>-5.17874</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>-80.6327</t>
+          <t>62</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>1018</t>
+          <t>-5.19625</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>-80.6379</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5771,32 +5771,32 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>410790</t>
+          <t>410276</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>ENRIQUE LOPEZ ALBUJAR</t>
+          <t>PNP BACILIO RAMIREZ PEÑA</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-5.19406</t>
+          <t>860</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>-80.64891</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>1064</t>
+          <t>-5.18797</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>-80.65006</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5833,37 +5833,37 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>833638</t>
+          <t>410262</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>VILLASOL</t>
+          <t>SELMIRA DE VARONA</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>-5.17193</t>
+          <t>934</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>-80.64448</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>-5.19173</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>-80.64987</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -5895,32 +5895,32 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>410827</t>
+          <t>410238</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE FATIMA</t>
+          <t>COMPLEJO LA ALBORADA</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>-5.19006</t>
+          <t>658</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>-80.6359</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>1902</t>
+          <t>-5.18634</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>-80.65428</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5957,32 +5957,32 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>775916</t>
+          <t>410115</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>SAN ANTONIO DE PADUA</t>
+          <t>225</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>-5.19186</t>
+          <t>78</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>-80.63122</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>-5.201211</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-80.632621</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6019,32 +6019,32 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>828646</t>
+          <t>409956</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>FEDERICO VILLARREAL</t>
+          <t>002</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>-5.20061</t>
+          <t>279</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>-80.62859</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>-5.18936</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>-80.63822</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6081,32 +6081,32 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>415170</t>
+          <t>409942</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>14138</t>
+          <t>001 MARIA CONCEPCION RAMOS CAMPOS</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>-4.7068</t>
+          <t>285</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>-80.1225</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>-5.19929</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-80.63386</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">

--- a/ZonasEscolares/excels/PIURA-PIURA-PIURA.xlsx
+++ b/ZonasEscolares/excels/PIURA-PIURA-PIURA.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
